--- a/runs/exp4_midterm/faculty_schedule.xlsx
+++ b/runs/exp4_midterm/faculty_schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e402f802124af4b/Masaüstü/Projects/Campus-Scheduling/runs/exp4_midterm/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="11_6EC121F23CD38B2FF92D4C47CD2D1F9D7979D445" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B10E608-CD44-4DD0-8C61-B8C911AC2685}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="11_6EC121F23CD38B2FF92D4C47CD2D1F9D7979D445" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B0DC5AFB-2DB2-46F8-A5D7-BE9FACD4CEBE}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,9 +25,6 @@
     <t>Departments</t>
   </si>
   <si>
-    <t>Year:</t>
-  </si>
-  <si>
     <t>Course ID</t>
   </si>
   <si>
@@ -1094,6 +1091,9 @@
   </si>
   <si>
     <t>capacity</t>
+  </si>
+  <si>
+    <t>Year</t>
   </si>
 </sst>
 </file>
@@ -1180,6 +1180,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1484,45 +1488,45 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>357</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="J1" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>356</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2">
         <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D2">
         <v>6</v>
@@ -1531,7 +1535,7 @@
         <v>2</v>
       </c>
       <c r="F2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1545,13 +1549,13 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3">
         <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D3">
         <v>3</v>
@@ -1560,7 +1564,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -1574,13 +1578,13 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B4">
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D4">
         <v>8</v>
@@ -1589,7 +1593,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G4">
         <v>3</v>
@@ -1603,13 +1607,13 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B5">
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D5">
         <v>9</v>
@@ -1618,7 +1622,7 @@
         <v>2</v>
       </c>
       <c r="F5" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -1632,13 +1636,13 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B6">
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D6">
         <v>10</v>
@@ -1647,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1661,13 +1665,13 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B7">
         <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D7">
         <v>8</v>
@@ -1676,7 +1680,7 @@
         <v>2</v>
       </c>
       <c r="F7" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -1690,13 +1694,13 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D8">
         <v>5</v>
@@ -1705,7 +1709,7 @@
         <v>2</v>
       </c>
       <c r="F8" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="G8">
         <v>4</v>
@@ -1719,13 +1723,13 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D9">
         <v>5</v>
@@ -1734,7 +1738,7 @@
         <v>2</v>
       </c>
       <c r="F9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -1748,13 +1752,13 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B10">
         <v>4</v>
       </c>
       <c r="C10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D10">
         <v>8</v>
@@ -1763,7 +1767,7 @@
         <v>0</v>
       </c>
       <c r="F10" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -1777,13 +1781,13 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B11">
         <v>4</v>
       </c>
       <c r="C11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D11">
         <v>10</v>
@@ -1792,7 +1796,7 @@
         <v>2</v>
       </c>
       <c r="F11" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -1806,13 +1810,13 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B12">
         <v>4</v>
       </c>
       <c r="C12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D12">
         <v>9</v>
@@ -1821,7 +1825,7 @@
         <v>5</v>
       </c>
       <c r="F12" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -1835,13 +1839,13 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B13">
         <v>3</v>
       </c>
       <c r="C13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D13">
         <v>2</v>
@@ -1850,7 +1854,7 @@
         <v>5</v>
       </c>
       <c r="F13" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -1864,13 +1868,13 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14">
         <v>3</v>
       </c>
       <c r="C14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D14">
         <v>3</v>
@@ -1879,7 +1883,7 @@
         <v>2</v>
       </c>
       <c r="F14" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G14">
         <v>4</v>
@@ -1893,13 +1897,13 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B15">
         <v>3</v>
       </c>
       <c r="C15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D15">
         <v>5</v>
@@ -1908,7 +1912,7 @@
         <v>0</v>
       </c>
       <c r="F15" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1922,13 +1926,13 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B16">
         <v>3</v>
       </c>
       <c r="C16" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -1937,7 +1941,7 @@
         <v>0</v>
       </c>
       <c r="F16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G16">
         <v>4</v>
@@ -1951,13 +1955,13 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B17">
         <v>2</v>
       </c>
       <c r="C17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D17">
         <v>9</v>
@@ -1966,7 +1970,7 @@
         <v>0</v>
       </c>
       <c r="F17" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1980,13 +1984,13 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B18">
         <v>1</v>
       </c>
       <c r="C18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -1995,7 +1999,7 @@
         <v>2</v>
       </c>
       <c r="F18" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G18">
         <v>4</v>
@@ -2009,13 +2013,13 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B19">
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D19">
         <v>3</v>
@@ -2024,7 +2028,7 @@
         <v>0</v>
       </c>
       <c r="F19" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G19">
         <v>4</v>
@@ -2038,13 +2042,13 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B20">
         <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D20">
         <v>3</v>
@@ -2053,7 +2057,7 @@
         <v>7</v>
       </c>
       <c r="F20" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G20">
         <v>3</v>
@@ -2067,13 +2071,13 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B21">
         <v>1</v>
       </c>
       <c r="C21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D21">
         <v>5</v>
@@ -2082,7 +2086,7 @@
         <v>7</v>
       </c>
       <c r="F21" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G21">
         <v>5</v>
@@ -2096,13 +2100,13 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B22">
         <v>3</v>
       </c>
       <c r="C22" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D22">
         <v>2</v>
@@ -2111,7 +2115,7 @@
         <v>2</v>
       </c>
       <c r="F22" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G22">
         <v>2</v>
@@ -2125,13 +2129,13 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B23">
         <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D23">
         <v>1</v>
@@ -2140,7 +2144,7 @@
         <v>2</v>
       </c>
       <c r="F23" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="G23">
         <v>2</v>
@@ -2154,13 +2158,13 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B24">
         <v>1</v>
       </c>
       <c r="C24" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D24">
         <v>4</v>
@@ -2169,7 +2173,7 @@
         <v>0</v>
       </c>
       <c r="F24" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G24">
         <v>4</v>
@@ -2183,13 +2187,13 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B25">
         <v>1</v>
       </c>
       <c r="C25" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D25">
         <v>4</v>
@@ -2198,7 +2202,7 @@
         <v>2</v>
       </c>
       <c r="F25" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -2212,13 +2216,13 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B26">
         <v>1</v>
       </c>
       <c r="C26" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D26">
         <v>1</v>
@@ -2227,7 +2231,7 @@
         <v>2</v>
       </c>
       <c r="F26" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G26">
         <v>2</v>
@@ -2241,13 +2245,13 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B27">
         <v>1</v>
       </c>
       <c r="C27" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D27">
         <v>4</v>
@@ -2256,7 +2260,7 @@
         <v>7</v>
       </c>
       <c r="F27" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G27">
         <v>6</v>
@@ -2270,13 +2274,13 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B28">
         <v>1</v>
       </c>
       <c r="C28" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D28">
         <v>1</v>
@@ -2285,7 +2289,7 @@
         <v>2</v>
       </c>
       <c r="F28" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G28">
         <v>1</v>
@@ -2299,13 +2303,13 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B29">
         <v>3</v>
       </c>
       <c r="C29" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D29">
         <v>1</v>
@@ -2314,7 +2318,7 @@
         <v>2</v>
       </c>
       <c r="F29" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -2328,13 +2332,13 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B30">
         <v>2</v>
       </c>
       <c r="C30" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D30">
         <v>10</v>
@@ -2343,7 +2347,7 @@
         <v>7</v>
       </c>
       <c r="F30" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G30">
         <v>2</v>
@@ -2357,13 +2361,13 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B31">
         <v>3</v>
       </c>
       <c r="C31" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D31">
         <v>5</v>
@@ -2372,7 +2376,7 @@
         <v>0</v>
       </c>
       <c r="F31" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G31">
         <v>1</v>
@@ -2386,13 +2390,13 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B32">
         <v>3</v>
       </c>
       <c r="C32" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D32">
         <v>2</v>
@@ -2401,7 +2405,7 @@
         <v>5</v>
       </c>
       <c r="F32" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="G32">
         <v>3</v>
@@ -2415,13 +2419,13 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B33">
         <v>3</v>
       </c>
       <c r="C33" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D33">
         <v>1</v>
@@ -2430,7 +2434,7 @@
         <v>7</v>
       </c>
       <c r="F33" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G33">
         <v>2</v>
@@ -2444,13 +2448,13 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B34">
         <v>2</v>
       </c>
       <c r="C34" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D34">
         <v>9</v>
@@ -2459,7 +2463,7 @@
         <v>2</v>
       </c>
       <c r="F34" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G34">
         <v>2</v>
@@ -2473,13 +2477,13 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B35">
         <v>4</v>
       </c>
       <c r="C35" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D35">
         <v>10</v>
@@ -2488,7 +2492,7 @@
         <v>2</v>
       </c>
       <c r="F35" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G35">
         <v>1</v>
@@ -2502,13 +2506,13 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B36">
         <v>3</v>
       </c>
       <c r="C36" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D36">
         <v>5</v>
@@ -2517,7 +2521,7 @@
         <v>2</v>
       </c>
       <c r="F36" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G36">
         <v>2</v>
@@ -2531,13 +2535,13 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B37">
         <v>2</v>
       </c>
       <c r="C37" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D37">
         <v>10</v>
@@ -2546,7 +2550,7 @@
         <v>0</v>
       </c>
       <c r="F37" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G37">
         <v>4</v>
@@ -2560,13 +2564,13 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B38">
         <v>1</v>
       </c>
       <c r="C38" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D38">
         <v>4</v>
@@ -2575,7 +2579,7 @@
         <v>2</v>
       </c>
       <c r="F38" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G38">
         <v>1</v>
@@ -2589,13 +2593,13 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B39">
         <v>1</v>
       </c>
       <c r="C39" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D39">
         <v>5</v>
@@ -2604,7 +2608,7 @@
         <v>6</v>
       </c>
       <c r="F39" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G39">
         <v>3</v>
@@ -2618,13 +2622,13 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B40">
         <v>1</v>
       </c>
       <c r="C40" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D40">
         <v>4</v>
@@ -2633,7 +2637,7 @@
         <v>0</v>
       </c>
       <c r="F40" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G40">
         <v>3</v>
@@ -2647,13 +2651,13 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B41">
         <v>4</v>
       </c>
       <c r="C41" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D41">
         <v>8</v>
@@ -2662,7 +2666,7 @@
         <v>5</v>
       </c>
       <c r="F41" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G41">
         <v>1</v>
@@ -2676,13 +2680,13 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B42">
         <v>4</v>
       </c>
       <c r="C42" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D42">
         <v>9</v>
@@ -2691,7 +2695,7 @@
         <v>7</v>
       </c>
       <c r="F42" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G42">
         <v>1</v>
@@ -2705,13 +2709,13 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B43">
         <v>3</v>
       </c>
       <c r="C43" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D43">
         <v>3</v>
@@ -2720,7 +2724,7 @@
         <v>5</v>
       </c>
       <c r="F43" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G43">
         <v>3</v>
@@ -2734,13 +2738,13 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B44">
         <v>1</v>
       </c>
       <c r="C44" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D44">
         <v>1</v>
@@ -2749,7 +2753,7 @@
         <v>2</v>
       </c>
       <c r="F44" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G44">
         <v>1</v>
@@ -2763,13 +2767,13 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B45">
         <v>3</v>
       </c>
       <c r="C45" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D45">
         <v>4</v>
@@ -2778,7 +2782,7 @@
         <v>7</v>
       </c>
       <c r="F45" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G45">
         <v>1</v>
@@ -2792,13 +2796,13 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B46">
         <v>2</v>
       </c>
       <c r="C46" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D46">
         <v>7</v>
@@ -2807,7 +2811,7 @@
         <v>2</v>
       </c>
       <c r="F46" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G46">
         <v>2</v>
@@ -2821,13 +2825,13 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B47">
         <v>2</v>
       </c>
       <c r="C47" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D47">
         <v>6</v>
@@ -2836,7 +2840,7 @@
         <v>5</v>
       </c>
       <c r="F47" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G47">
         <v>3</v>
@@ -2850,13 +2854,13 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B48">
         <v>4</v>
       </c>
       <c r="C48" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D48">
         <v>6</v>
@@ -2865,7 +2869,7 @@
         <v>7</v>
       </c>
       <c r="F48" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G48">
         <v>1</v>
@@ -2879,13 +2883,13 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B49">
         <v>1</v>
       </c>
       <c r="C49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D49">
         <v>2</v>
@@ -2894,7 +2898,7 @@
         <v>0</v>
       </c>
       <c r="F49" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G49">
         <v>3</v>
@@ -2908,13 +2912,13 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B50">
         <v>2</v>
       </c>
       <c r="C50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D50">
         <v>7</v>
@@ -2923,7 +2927,7 @@
         <v>5</v>
       </c>
       <c r="F50" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G50">
         <v>4</v>
@@ -2937,13 +2941,13 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B51">
         <v>2</v>
       </c>
       <c r="C51" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D51">
         <v>10</v>
@@ -2952,7 +2956,7 @@
         <v>2</v>
       </c>
       <c r="F51" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G51">
         <v>3</v>
@@ -2966,13 +2970,13 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B52">
         <v>2</v>
       </c>
       <c r="C52" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D52">
         <v>7</v>
@@ -2981,7 +2985,7 @@
         <v>7</v>
       </c>
       <c r="F52" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G52">
         <v>2</v>
@@ -2995,13 +2999,13 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B53">
         <v>2</v>
       </c>
       <c r="C53" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D53">
         <v>8</v>
@@ -3010,7 +3014,7 @@
         <v>2</v>
       </c>
       <c r="F53" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G53">
         <v>3</v>
@@ -3024,13 +3028,13 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B54">
         <v>2</v>
       </c>
       <c r="C54" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D54">
         <v>6</v>
@@ -3039,7 +3043,7 @@
         <v>7</v>
       </c>
       <c r="F54" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="G54">
         <v>4</v>
@@ -3053,13 +3057,13 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B55">
         <v>2</v>
       </c>
       <c r="C55" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D55">
         <v>6</v>
@@ -3068,7 +3072,7 @@
         <v>0</v>
       </c>
       <c r="F55" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G55">
         <v>3</v>
@@ -3082,13 +3086,13 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B56">
         <v>3</v>
       </c>
       <c r="C56" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D56">
         <v>1</v>
@@ -3097,7 +3101,7 @@
         <v>2</v>
       </c>
       <c r="F56" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="G56">
         <v>3</v>
@@ -3111,13 +3115,13 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B57">
         <v>2</v>
       </c>
       <c r="C57" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D57">
         <v>6</v>
@@ -3126,7 +3130,7 @@
         <v>2</v>
       </c>
       <c r="F57" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G57">
         <v>5</v>
@@ -3140,13 +3144,13 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B58">
         <v>4</v>
       </c>
       <c r="C58" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D58">
         <v>7</v>
@@ -3155,7 +3159,7 @@
         <v>5</v>
       </c>
       <c r="F58" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="G58">
         <v>1</v>
@@ -3169,13 +3173,13 @@
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B59">
         <v>2</v>
       </c>
       <c r="C59" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D59">
         <v>6</v>
@@ -3184,7 +3188,7 @@
         <v>0</v>
       </c>
       <c r="F59" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G59">
         <v>4</v>
@@ -3198,13 +3202,13 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B60">
         <v>4</v>
       </c>
       <c r="C60" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D60">
         <v>6</v>
@@ -3213,7 +3217,7 @@
         <v>0</v>
       </c>
       <c r="F60" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="G60">
         <v>3</v>
@@ -3227,13 +3231,13 @@
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B61">
         <v>2</v>
       </c>
       <c r="C61" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D61">
         <v>8</v>
@@ -3242,7 +3246,7 @@
         <v>5</v>
       </c>
       <c r="F61" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G61">
         <v>5</v>
@@ -3256,13 +3260,13 @@
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B62">
         <v>2</v>
       </c>
       <c r="C62" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D62">
         <v>9</v>
@@ -3271,7 +3275,7 @@
         <v>5</v>
       </c>
       <c r="F62" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G62">
         <v>2</v>
@@ -3285,13 +3289,13 @@
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B63">
         <v>4</v>
       </c>
       <c r="C63" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D63">
         <v>10</v>
@@ -3300,7 +3304,7 @@
         <v>7</v>
       </c>
       <c r="F63" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G63">
         <v>2</v>
@@ -3314,13 +3318,13 @@
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B64">
         <v>4</v>
       </c>
       <c r="C64" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D64">
         <v>7</v>
@@ -3329,7 +3333,7 @@
         <v>0</v>
       </c>
       <c r="F64" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G64">
         <v>1</v>
@@ -3343,13 +3347,13 @@
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B65">
         <v>4</v>
       </c>
       <c r="C65" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D65">
         <v>7</v>
@@ -3358,7 +3362,7 @@
         <v>2</v>
       </c>
       <c r="F65" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G65">
         <v>1</v>
@@ -3372,13 +3376,13 @@
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B66">
         <v>4</v>
       </c>
       <c r="C66" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D66">
         <v>7</v>
@@ -3387,7 +3391,7 @@
         <v>2</v>
       </c>
       <c r="F66" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G66">
         <v>1</v>
@@ -3401,13 +3405,13 @@
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B67">
         <v>2</v>
       </c>
       <c r="C67" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D67">
         <v>8</v>
@@ -3416,7 +3420,7 @@
         <v>2</v>
       </c>
       <c r="F67" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="G67">
         <v>3</v>
@@ -3430,13 +3434,13 @@
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B68">
         <v>4</v>
       </c>
       <c r="C68" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D68">
         <v>7</v>
@@ -3445,7 +3449,7 @@
         <v>0</v>
       </c>
       <c r="F68" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="G68">
         <v>2</v>
@@ -3459,13 +3463,13 @@
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B69">
         <v>3</v>
       </c>
       <c r="C69" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D69">
         <v>5</v>
@@ -3474,7 +3478,7 @@
         <v>2</v>
       </c>
       <c r="F69" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="G69">
         <v>3</v>
@@ -3488,13 +3492,13 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B70">
         <v>1</v>
       </c>
       <c r="C70" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D70">
         <v>3</v>
@@ -3503,7 +3507,7 @@
         <v>5</v>
       </c>
       <c r="F70" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G70">
         <v>1</v>
@@ -3517,13 +3521,13 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B71">
         <v>2</v>
       </c>
       <c r="C71" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D71">
         <v>10</v>
@@ -3532,7 +3536,7 @@
         <v>2</v>
       </c>
       <c r="F71" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G71">
         <v>2</v>
@@ -3546,13 +3550,13 @@
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B72">
         <v>2</v>
       </c>
       <c r="C72" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D72">
         <v>6</v>
@@ -3561,7 +3565,7 @@
         <v>7</v>
       </c>
       <c r="F72" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="G72">
         <v>1</v>
@@ -3575,13 +3579,13 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B73">
         <v>3</v>
       </c>
       <c r="C73" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D73">
         <v>3</v>
@@ -3590,7 +3594,7 @@
         <v>7</v>
       </c>
       <c r="F73" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G73">
         <v>1</v>
@@ -3604,13 +3608,13 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B74">
         <v>3</v>
       </c>
       <c r="C74" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D74">
         <v>5</v>
@@ -3619,7 +3623,7 @@
         <v>2</v>
       </c>
       <c r="F74" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="G74">
         <v>4</v>
@@ -3633,13 +3637,13 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B75">
         <v>1</v>
       </c>
       <c r="C75" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D75">
         <v>3</v>
@@ -3648,7 +3652,7 @@
         <v>0</v>
       </c>
       <c r="F75" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="G75">
         <v>4</v>
@@ -3662,13 +3666,13 @@
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B76">
         <v>3</v>
       </c>
       <c r="C76" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D76">
         <v>2</v>
@@ -3677,7 +3681,7 @@
         <v>2</v>
       </c>
       <c r="F76" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="G76">
         <v>3</v>
@@ -3691,13 +3695,13 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B77">
         <v>1</v>
       </c>
       <c r="C77" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D77">
         <v>4</v>
@@ -3706,7 +3710,7 @@
         <v>0</v>
       </c>
       <c r="F77" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="G77">
         <v>3</v>
@@ -3720,13 +3724,13 @@
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B78">
         <v>4</v>
       </c>
       <c r="C78" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D78">
         <v>8</v>
@@ -3735,7 +3739,7 @@
         <v>5</v>
       </c>
       <c r="F78" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G78">
         <v>1</v>
@@ -3749,13 +3753,13 @@
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B79">
         <v>3</v>
       </c>
       <c r="C79" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D79">
         <v>3</v>
@@ -3764,7 +3768,7 @@
         <v>2</v>
       </c>
       <c r="F79" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="G79">
         <v>1</v>
@@ -3778,13 +3782,13 @@
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B80">
         <v>1</v>
       </c>
       <c r="C80" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D80">
         <v>2</v>
@@ -3793,7 +3797,7 @@
         <v>0</v>
       </c>
       <c r="F80" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G80">
         <v>1</v>
@@ -3807,13 +3811,13 @@
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B81">
         <v>4</v>
       </c>
       <c r="C81" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D81">
         <v>7</v>
@@ -3822,7 +3826,7 @@
         <v>0</v>
       </c>
       <c r="F81" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G81">
         <v>1</v>
@@ -3836,13 +3840,13 @@
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B82">
         <v>4</v>
       </c>
       <c r="C82" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D82">
         <v>9</v>
@@ -3851,7 +3855,7 @@
         <v>0</v>
       </c>
       <c r="F82" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G82">
         <v>2</v>
@@ -3865,13 +3869,13 @@
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B83">
         <v>4</v>
       </c>
       <c r="C83" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D83">
         <v>6</v>
@@ -3880,7 +3884,7 @@
         <v>5</v>
       </c>
       <c r="F83" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="G83">
         <v>2</v>
@@ -3894,13 +3898,13 @@
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B84">
         <v>4</v>
       </c>
       <c r="C84" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D84">
         <v>8</v>
@@ -3909,7 +3913,7 @@
         <v>0</v>
       </c>
       <c r="F84" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G84">
         <v>1</v>
@@ -3923,13 +3927,13 @@
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B85">
         <v>4</v>
       </c>
       <c r="C85" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D85">
         <v>8</v>
@@ -3938,7 +3942,7 @@
         <v>5</v>
       </c>
       <c r="F85" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="G85">
         <v>2</v>
@@ -3952,13 +3956,13 @@
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B86">
         <v>2</v>
       </c>
       <c r="C86" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D86">
         <v>6</v>
@@ -3967,7 +3971,7 @@
         <v>0</v>
       </c>
       <c r="F86" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="G86">
         <v>2</v>
@@ -3981,13 +3985,13 @@
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A87" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B87">
         <v>2</v>
       </c>
       <c r="C87" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D87">
         <v>8</v>
@@ -3996,7 +4000,7 @@
         <v>5</v>
       </c>
       <c r="F87" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G87">
         <v>2</v>
@@ -4010,13 +4014,13 @@
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B88">
         <v>2</v>
       </c>
       <c r="C88" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D88">
         <v>9</v>
@@ -4025,7 +4029,7 @@
         <v>2</v>
       </c>
       <c r="F88" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="G88">
         <v>2</v>
@@ -4039,13 +4043,13 @@
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B89">
         <v>2</v>
       </c>
       <c r="C89" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D89">
         <v>8</v>
@@ -4054,7 +4058,7 @@
         <v>2</v>
       </c>
       <c r="F89" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G89">
         <v>1</v>
@@ -4068,13 +4072,13 @@
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A90" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B90">
         <v>4</v>
       </c>
       <c r="C90" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D90">
         <v>6</v>
@@ -4083,7 +4087,7 @@
         <v>7</v>
       </c>
       <c r="F90" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="G90">
         <v>1</v>
@@ -4097,13 +4101,13 @@
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B91">
         <v>4</v>
       </c>
       <c r="C91" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D91">
         <v>10</v>
@@ -4112,7 +4116,7 @@
         <v>2</v>
       </c>
       <c r="F91" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="G91">
         <v>2</v>
@@ -4126,13 +4130,13 @@
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A92" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B92">
         <v>3</v>
       </c>
       <c r="C92" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D92">
         <v>3</v>
@@ -4141,7 +4145,7 @@
         <v>0</v>
       </c>
       <c r="F92" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G92">
         <v>3</v>
@@ -4155,13 +4159,13 @@
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A93" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B93">
         <v>3</v>
       </c>
       <c r="C93" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D93">
         <v>1</v>
@@ -4170,7 +4174,7 @@
         <v>2</v>
       </c>
       <c r="F93" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G93">
         <v>3</v>
@@ -4184,13 +4188,13 @@
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A94" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B94">
         <v>3</v>
       </c>
       <c r="C94" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D94">
         <v>2</v>
@@ -4199,7 +4203,7 @@
         <v>5</v>
       </c>
       <c r="F94" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G94">
         <v>1</v>
@@ -4213,13 +4217,13 @@
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A95" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B95">
         <v>2</v>
       </c>
       <c r="C95" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D95">
         <v>8</v>
@@ -4228,7 +4232,7 @@
         <v>0</v>
       </c>
       <c r="F95" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G95">
         <v>1</v>
@@ -4242,13 +4246,13 @@
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A96" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B96">
         <v>3</v>
       </c>
       <c r="C96" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D96">
         <v>3</v>
@@ -4257,7 +4261,7 @@
         <v>2</v>
       </c>
       <c r="F96" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G96">
         <v>3</v>
@@ -4271,13 +4275,13 @@
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A97" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B97">
         <v>3</v>
       </c>
       <c r="C97" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D97">
         <v>3</v>
@@ -4286,7 +4290,7 @@
         <v>0</v>
       </c>
       <c r="F97" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G97">
         <v>1</v>
@@ -4300,13 +4304,13 @@
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A98" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B98">
         <v>2</v>
       </c>
       <c r="C98" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D98">
         <v>7</v>
@@ -4315,7 +4319,7 @@
         <v>5</v>
       </c>
       <c r="F98" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G98">
         <v>1</v>
@@ -4329,13 +4333,13 @@
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A99" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B99">
         <v>4</v>
       </c>
       <c r="C99" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D99">
         <v>6</v>
@@ -4344,7 +4348,7 @@
         <v>5</v>
       </c>
       <c r="F99" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G99">
         <v>1</v>
@@ -4358,13 +4362,13 @@
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A100" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B100">
         <v>3</v>
       </c>
       <c r="C100" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D100">
         <v>5</v>
@@ -4373,7 +4377,7 @@
         <v>6</v>
       </c>
       <c r="F100" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G100">
         <v>1</v>
@@ -4387,13 +4391,13 @@
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A101" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B101">
         <v>3</v>
       </c>
       <c r="C101" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D101">
         <v>2</v>
@@ -4402,7 +4406,7 @@
         <v>2</v>
       </c>
       <c r="F101" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="G101">
         <v>2</v>
@@ -4416,13 +4420,13 @@
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A102" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B102">
         <v>4</v>
       </c>
       <c r="C102" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D102">
         <v>6</v>
@@ -4431,7 +4435,7 @@
         <v>7</v>
       </c>
       <c r="F102" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G102">
         <v>1</v>
@@ -4445,13 +4449,13 @@
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A103" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B103">
         <v>4</v>
       </c>
       <c r="C103" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D103">
         <v>8</v>
@@ -4460,7 +4464,7 @@
         <v>0</v>
       </c>
       <c r="F103" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G103">
         <v>1</v>
@@ -4474,13 +4478,13 @@
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A104" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B104">
         <v>3</v>
       </c>
       <c r="C104" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D104">
         <v>3</v>
@@ -4489,7 +4493,7 @@
         <v>7</v>
       </c>
       <c r="F104" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G104">
         <v>1</v>
@@ -4503,13 +4507,13 @@
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A105" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B105">
         <v>4</v>
       </c>
       <c r="C105" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D105">
         <v>7</v>
@@ -4518,7 +4522,7 @@
         <v>7</v>
       </c>
       <c r="F105" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G105">
         <v>1</v>
@@ -4532,13 +4536,13 @@
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A106" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B106">
         <v>3</v>
       </c>
       <c r="C106" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D106">
         <v>4</v>
@@ -4547,7 +4551,7 @@
         <v>7</v>
       </c>
       <c r="F106" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="G106">
         <v>3</v>
@@ -4561,13 +4565,13 @@
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A107" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B107">
         <v>4</v>
       </c>
       <c r="C107" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D107">
         <v>9</v>
@@ -4576,7 +4580,7 @@
         <v>5</v>
       </c>
       <c r="F107" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="G107">
         <v>2</v>
@@ -4590,13 +4594,13 @@
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A108" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B108">
         <v>3</v>
       </c>
       <c r="C108" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D108">
         <v>1</v>
@@ -4605,7 +4609,7 @@
         <v>0</v>
       </c>
       <c r="F108" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G108">
         <v>1</v>
@@ -4619,13 +4623,13 @@
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A109" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B109">
         <v>3</v>
       </c>
       <c r="C109" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D109">
         <v>1</v>
@@ -4634,7 +4638,7 @@
         <v>0</v>
       </c>
       <c r="F109" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G109">
         <v>2</v>
@@ -4648,13 +4652,13 @@
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A110" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B110">
         <v>3</v>
       </c>
       <c r="C110" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D110">
         <v>4</v>
@@ -4663,7 +4667,7 @@
         <v>0</v>
       </c>
       <c r="F110" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="G110">
         <v>2</v>
@@ -4677,13 +4681,13 @@
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A111" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B111">
         <v>1</v>
       </c>
       <c r="C111" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D111">
         <v>5</v>
@@ -4692,7 +4696,7 @@
         <v>7</v>
       </c>
       <c r="F111" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="G111">
         <v>5</v>
@@ -4706,13 +4710,13 @@
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A112" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B112">
         <v>2</v>
       </c>
       <c r="C112" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D112">
         <v>7</v>
@@ -4721,7 +4725,7 @@
         <v>7</v>
       </c>
       <c r="F112" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="G112">
         <v>1</v>
@@ -4735,13 +4739,13 @@
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A113" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B113">
         <v>4</v>
       </c>
       <c r="C113" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D113">
         <v>9</v>
@@ -4750,7 +4754,7 @@
         <v>5</v>
       </c>
       <c r="F113" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="G113">
         <v>2</v>
@@ -4764,13 +4768,13 @@
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A114" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B114">
         <v>4</v>
       </c>
       <c r="C114" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D114">
         <v>8</v>
@@ -4779,7 +4783,7 @@
         <v>2</v>
       </c>
       <c r="F114" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G114">
         <v>1</v>
@@ -4793,13 +4797,13 @@
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A115" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B115">
         <v>3</v>
       </c>
       <c r="C115" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D115">
         <v>2</v>
@@ -4808,7 +4812,7 @@
         <v>7</v>
       </c>
       <c r="F115" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G115">
         <v>1</v>
@@ -4822,13 +4826,13 @@
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A116" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B116">
         <v>4</v>
       </c>
       <c r="C116" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D116">
         <v>6</v>
@@ -4837,7 +4841,7 @@
         <v>0</v>
       </c>
       <c r="F116" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G116">
         <v>1</v>
@@ -4851,13 +4855,13 @@
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A117" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B117">
         <v>2</v>
       </c>
       <c r="C117" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D117">
         <v>7</v>
@@ -4866,7 +4870,7 @@
         <v>0</v>
       </c>
       <c r="F117" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G117">
         <v>1</v>
@@ -4880,13 +4884,13 @@
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A118" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B118">
         <v>3</v>
       </c>
       <c r="C118" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D118">
         <v>1</v>
@@ -4895,7 +4899,7 @@
         <v>2</v>
       </c>
       <c r="F118" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G118">
         <v>1</v>
@@ -4909,13 +4913,13 @@
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A119" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B119">
         <v>3</v>
       </c>
       <c r="C119" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D119">
         <v>3</v>
@@ -4924,7 +4928,7 @@
         <v>2</v>
       </c>
       <c r="F119" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="G119">
         <v>1</v>
@@ -4938,13 +4942,13 @@
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A120" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B120">
         <v>2</v>
       </c>
       <c r="C120" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D120">
         <v>7</v>
@@ -4953,7 +4957,7 @@
         <v>5</v>
       </c>
       <c r="F120" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G120">
         <v>1</v>
@@ -4967,13 +4971,13 @@
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A121" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B121">
         <v>1</v>
       </c>
       <c r="C121" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D121">
         <v>4</v>
@@ -4982,7 +4986,7 @@
         <v>5</v>
       </c>
       <c r="F121" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G121">
         <v>2</v>
@@ -4996,13 +5000,13 @@
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A122" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B122">
         <v>1</v>
       </c>
       <c r="C122" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D122">
         <v>2</v>
@@ -5011,7 +5015,7 @@
         <v>2</v>
       </c>
       <c r="F122" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="G122">
         <v>2</v>
@@ -5025,13 +5029,13 @@
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A123" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B123">
         <v>1</v>
       </c>
       <c r="C123" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D123">
         <v>2</v>
@@ -5040,7 +5044,7 @@
         <v>7</v>
       </c>
       <c r="F123" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G123">
         <v>2</v>
@@ -5054,13 +5058,13 @@
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A124" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B124">
         <v>4</v>
       </c>
       <c r="C124" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D124">
         <v>9</v>
@@ -5069,7 +5073,7 @@
         <v>5</v>
       </c>
       <c r="F124" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G124">
         <v>1</v>
@@ -5083,13 +5087,13 @@
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A125" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B125">
         <v>4</v>
       </c>
       <c r="C125" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D125">
         <v>6</v>
@@ -5098,7 +5102,7 @@
         <v>5</v>
       </c>
       <c r="F125" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G125">
         <v>1</v>
@@ -5112,13 +5116,13 @@
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A126" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B126">
         <v>4</v>
       </c>
       <c r="C126" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D126">
         <v>8</v>
@@ -5127,7 +5131,7 @@
         <v>5</v>
       </c>
       <c r="F126" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G126">
         <v>1</v>
@@ -5141,13 +5145,13 @@
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A127" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B127">
         <v>2</v>
       </c>
       <c r="C127" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D127">
         <v>9</v>
@@ -5156,7 +5160,7 @@
         <v>0</v>
       </c>
       <c r="F127" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="G127">
         <v>4</v>
@@ -5170,13 +5174,13 @@
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A128" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B128">
         <v>1</v>
       </c>
       <c r="C128" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D128">
         <v>5</v>
@@ -5185,7 +5189,7 @@
         <v>0</v>
       </c>
       <c r="F128" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="G128">
         <v>5</v>
@@ -5199,13 +5203,13 @@
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A129" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B129">
         <v>1</v>
       </c>
       <c r="C129" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D129">
         <v>4</v>
@@ -5214,7 +5218,7 @@
         <v>5</v>
       </c>
       <c r="F129" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="G129">
         <v>3</v>
@@ -5228,13 +5232,13 @@
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A130" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B130">
         <v>4</v>
       </c>
       <c r="C130" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D130">
         <v>7</v>
@@ -5243,7 +5247,7 @@
         <v>2</v>
       </c>
       <c r="F130" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G130">
         <v>1</v>
@@ -5257,13 +5261,13 @@
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A131" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B131">
         <v>4</v>
       </c>
       <c r="C131" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D131">
         <v>8</v>
@@ -5272,7 +5276,7 @@
         <v>0</v>
       </c>
       <c r="F131" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G131">
         <v>1</v>
@@ -5286,13 +5290,13 @@
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A132" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B132">
         <v>2</v>
       </c>
       <c r="C132" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D132">
         <v>6</v>
@@ -5301,7 +5305,7 @@
         <v>7</v>
       </c>
       <c r="F132" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G132">
         <v>1</v>
@@ -5315,13 +5319,13 @@
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A133" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B133">
         <v>4</v>
       </c>
       <c r="C133" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D133">
         <v>10</v>
@@ -5330,7 +5334,7 @@
         <v>7</v>
       </c>
       <c r="F133" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G133">
         <v>1</v>
@@ -5344,13 +5348,13 @@
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A134" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B134">
         <v>4</v>
       </c>
       <c r="C134" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D134">
         <v>9</v>
@@ -5359,7 +5363,7 @@
         <v>0</v>
       </c>
       <c r="F134" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G134">
         <v>1</v>
@@ -5373,13 +5377,13 @@
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A135" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B135">
         <v>1</v>
       </c>
       <c r="C135" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D135">
         <v>5</v>
@@ -5388,7 +5392,7 @@
         <v>2</v>
       </c>
       <c r="F135" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G135">
         <v>4</v>
@@ -5402,13 +5406,13 @@
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A136" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B136">
         <v>4</v>
       </c>
       <c r="C136" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D136">
         <v>7</v>
@@ -5417,7 +5421,7 @@
         <v>5</v>
       </c>
       <c r="F136" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G136">
         <v>1</v>
@@ -5431,13 +5435,13 @@
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A137" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B137">
         <v>1</v>
       </c>
       <c r="C137" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D137">
         <v>5</v>
@@ -5446,7 +5450,7 @@
         <v>7</v>
       </c>
       <c r="F137" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G137">
         <v>2</v>
@@ -5460,13 +5464,13 @@
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A138" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B138">
         <v>1</v>
       </c>
       <c r="C138" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D138">
         <v>1</v>
@@ -5475,7 +5479,7 @@
         <v>0</v>
       </c>
       <c r="F138" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G138">
         <v>5</v>
@@ -5489,13 +5493,13 @@
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A139" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B139">
         <v>1</v>
       </c>
       <c r="C139" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D139">
         <v>2</v>
@@ -5504,7 +5508,7 @@
         <v>5</v>
       </c>
       <c r="F139" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G139">
         <v>6</v>
@@ -5518,13 +5522,13 @@
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A140" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B140">
         <v>4</v>
       </c>
       <c r="C140" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D140">
         <v>6</v>
@@ -5533,7 +5537,7 @@
         <v>2</v>
       </c>
       <c r="F140" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G140">
         <v>2</v>
@@ -5547,13 +5551,13 @@
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A141" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B141">
         <v>3</v>
       </c>
       <c r="C141" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D141">
         <v>4</v>
@@ -5562,7 +5566,7 @@
         <v>7</v>
       </c>
       <c r="F141" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G141">
         <v>1</v>
@@ -5576,13 +5580,13 @@
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A142" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B142">
         <v>4</v>
       </c>
       <c r="C142" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D142">
         <v>9</v>
@@ -5591,7 +5595,7 @@
         <v>0</v>
       </c>
       <c r="F142" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G142">
         <v>2</v>
@@ -5605,13 +5609,13 @@
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A143" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B143">
         <v>4</v>
       </c>
       <c r="C143" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D143">
         <v>7</v>
@@ -5620,7 +5624,7 @@
         <v>2</v>
       </c>
       <c r="F143" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G143">
         <v>1</v>
@@ -5634,13 +5638,13 @@
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A144" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B144">
         <v>3</v>
       </c>
       <c r="C144" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D144">
         <v>3</v>
@@ -5649,7 +5653,7 @@
         <v>5</v>
       </c>
       <c r="F144" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G144">
         <v>1</v>
@@ -5663,13 +5667,13 @@
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A145" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B145">
         <v>4</v>
       </c>
       <c r="C145" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D145">
         <v>6</v>
@@ -5678,7 +5682,7 @@
         <v>2</v>
       </c>
       <c r="F145" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G145">
         <v>1</v>
@@ -5692,13 +5696,13 @@
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A146" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B146">
         <v>2</v>
       </c>
       <c r="C146" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D146">
         <v>10</v>
@@ -5707,7 +5711,7 @@
         <v>0</v>
       </c>
       <c r="F146" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G146">
         <v>1</v>
@@ -5721,13 +5725,13 @@
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A147" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B147">
         <v>3</v>
       </c>
       <c r="C147" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D147">
         <v>2</v>
@@ -5736,7 +5740,7 @@
         <v>0</v>
       </c>
       <c r="F147" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G147">
         <v>1</v>
@@ -5750,13 +5754,13 @@
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A148" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B148">
         <v>4</v>
       </c>
       <c r="C148" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D148">
         <v>10</v>
@@ -5765,7 +5769,7 @@
         <v>7</v>
       </c>
       <c r="F148" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G148">
         <v>1</v>
@@ -5779,13 +5783,13 @@
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A149" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B149">
         <v>2</v>
       </c>
       <c r="C149" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D149">
         <v>7</v>
@@ -5794,7 +5798,7 @@
         <v>0</v>
       </c>
       <c r="F149" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G149">
         <v>2</v>
@@ -5808,13 +5812,13 @@
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A150" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B150">
         <v>4</v>
       </c>
       <c r="C150" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D150">
         <v>6</v>
@@ -5823,7 +5827,7 @@
         <v>7</v>
       </c>
       <c r="F150" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G150">
         <v>1</v>
@@ -5837,13 +5841,13 @@
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A151" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B151">
         <v>4</v>
       </c>
       <c r="C151" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D151">
         <v>9</v>
@@ -5852,7 +5856,7 @@
         <v>7</v>
       </c>
       <c r="F151" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G151">
         <v>1</v>
@@ -5866,13 +5870,13 @@
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A152" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B152">
         <v>4</v>
       </c>
       <c r="C152" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D152">
         <v>8</v>
@@ -5881,7 +5885,7 @@
         <v>2</v>
       </c>
       <c r="F152" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G152">
         <v>1</v>
@@ -5895,13 +5899,13 @@
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A153" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B153">
         <v>4</v>
       </c>
       <c r="C153" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D153">
         <v>9</v>
@@ -5910,7 +5914,7 @@
         <v>0</v>
       </c>
       <c r="F153" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G153">
         <v>1</v>
@@ -5924,13 +5928,13 @@
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A154" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B154">
         <v>2</v>
       </c>
       <c r="C154" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D154">
         <v>10</v>
@@ -5939,7 +5943,7 @@
         <v>7</v>
       </c>
       <c r="F154" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G154">
         <v>2</v>
@@ -5953,13 +5957,13 @@
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A155" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B155">
         <v>2</v>
       </c>
       <c r="C155" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D155">
         <v>10</v>
@@ -5968,7 +5972,7 @@
         <v>2</v>
       </c>
       <c r="F155" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G155">
         <v>1</v>
@@ -5982,13 +5986,13 @@
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A156" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B156">
         <v>3</v>
       </c>
       <c r="C156" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D156">
         <v>5</v>
@@ -5997,7 +6001,7 @@
         <v>2</v>
       </c>
       <c r="F156" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G156">
         <v>1</v>
@@ -6011,13 +6015,13 @@
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A157" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B157">
         <v>1</v>
       </c>
       <c r="C157" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D157">
         <v>3</v>
@@ -6026,7 +6030,7 @@
         <v>2</v>
       </c>
       <c r="F157" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G157">
         <v>3</v>
@@ -6040,13 +6044,13 @@
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A158" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B158">
         <v>3</v>
       </c>
       <c r="C158" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D158">
         <v>1</v>
@@ -6055,7 +6059,7 @@
         <v>0</v>
       </c>
       <c r="F158" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G158">
         <v>4</v>
@@ -6069,13 +6073,13 @@
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A159" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B159">
         <v>3</v>
       </c>
       <c r="C159" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D159">
         <v>2</v>
@@ -6084,7 +6088,7 @@
         <v>0</v>
       </c>
       <c r="F159" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G159">
         <v>1</v>
@@ -6098,13 +6102,13 @@
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A160" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B160">
         <v>4</v>
       </c>
       <c r="C160" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D160">
         <v>7</v>
@@ -6113,7 +6117,7 @@
         <v>0</v>
       </c>
       <c r="F160" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G160">
         <v>1</v>
@@ -6127,13 +6131,13 @@
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A161" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B161">
         <v>4</v>
       </c>
       <c r="C161" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D161">
         <v>10</v>
@@ -6142,7 +6146,7 @@
         <v>0</v>
       </c>
       <c r="F161" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G161">
         <v>1</v>
@@ -6156,13 +6160,13 @@
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A162" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B162">
         <v>1</v>
       </c>
       <c r="C162" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D162">
         <v>1</v>
@@ -6171,7 +6175,7 @@
         <v>7</v>
       </c>
       <c r="F162" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="G162">
         <v>8</v>
@@ -6185,13 +6189,13 @@
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A163" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B163">
         <v>1</v>
       </c>
       <c r="C163" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D163">
         <v>5</v>
@@ -6200,7 +6204,7 @@
         <v>0</v>
       </c>
       <c r="F163" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G163">
         <v>1</v>
@@ -6214,13 +6218,13 @@
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A164" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B164">
         <v>4</v>
       </c>
       <c r="C164" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D164">
         <v>10</v>
@@ -6229,7 +6233,7 @@
         <v>0</v>
       </c>
       <c r="F164" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="G164">
         <v>2</v>
@@ -6243,13 +6247,13 @@
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A165" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B165">
         <v>3</v>
       </c>
       <c r="C165" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D165">
         <v>1</v>
@@ -6258,7 +6262,7 @@
         <v>5</v>
       </c>
       <c r="F165" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="G165">
         <v>3</v>
@@ -6272,13 +6276,13 @@
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A166" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B166">
         <v>3</v>
       </c>
       <c r="C166" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D166">
         <v>4</v>
@@ -6287,7 +6291,7 @@
         <v>2</v>
       </c>
       <c r="F166" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="G166">
         <v>2</v>
@@ -6301,13 +6305,13 @@
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A167" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B167">
         <v>4</v>
       </c>
       <c r="C167" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D167">
         <v>9</v>
@@ -6316,7 +6320,7 @@
         <v>0</v>
       </c>
       <c r="F167" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G167">
         <v>1</v>
@@ -6330,13 +6334,13 @@
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A168" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B168">
         <v>4</v>
       </c>
       <c r="C168" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D168">
         <v>10</v>
@@ -6345,7 +6349,7 @@
         <v>7</v>
       </c>
       <c r="F168" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="G168">
         <v>2</v>
@@ -6359,13 +6363,13 @@
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A169" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B169">
         <v>4</v>
       </c>
       <c r="C169" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D169">
         <v>9</v>
@@ -6374,7 +6378,7 @@
         <v>2</v>
       </c>
       <c r="F169" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="G169">
         <v>2</v>
@@ -6388,13 +6392,13 @@
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A170" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B170">
         <v>4</v>
       </c>
       <c r="C170" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D170">
         <v>6</v>
@@ -6403,7 +6407,7 @@
         <v>2</v>
       </c>
       <c r="F170" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G170">
         <v>1</v>
@@ -6417,13 +6421,13 @@
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A171" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B171">
         <v>3</v>
       </c>
       <c r="C171" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D171">
         <v>5</v>
@@ -6432,7 +6436,7 @@
         <v>0</v>
       </c>
       <c r="F171" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G171">
         <v>4</v>
@@ -6446,13 +6450,13 @@
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A172" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B172">
         <v>4</v>
       </c>
       <c r="C172" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D172">
         <v>8</v>
@@ -6461,7 +6465,7 @@
         <v>5</v>
       </c>
       <c r="F172" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G172">
         <v>1</v>
@@ -6475,13 +6479,13 @@
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A173" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B173">
         <v>3</v>
       </c>
       <c r="C173" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D173">
         <v>1</v>
@@ -6490,7 +6494,7 @@
         <v>0</v>
       </c>
       <c r="F173" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G173">
         <v>1</v>
@@ -6504,13 +6508,13 @@
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A174" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B174">
         <v>4</v>
       </c>
       <c r="C174" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D174">
         <v>7</v>
@@ -6519,7 +6523,7 @@
         <v>7</v>
       </c>
       <c r="F174" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="G174">
         <v>2</v>
@@ -6533,13 +6537,13 @@
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A175" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B175">
         <v>2</v>
       </c>
       <c r="C175" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D175">
         <v>6</v>
@@ -6548,7 +6552,7 @@
         <v>2</v>
       </c>
       <c r="F175" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G175">
         <v>1</v>
@@ -6562,13 +6566,13 @@
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A176" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B176">
         <v>3</v>
       </c>
       <c r="C176" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D176">
         <v>2</v>
@@ -6577,7 +6581,7 @@
         <v>2</v>
       </c>
       <c r="F176" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G176">
         <v>2</v>
@@ -6591,13 +6595,13 @@
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A177" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B177">
         <v>4</v>
       </c>
       <c r="C177" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D177">
         <v>9</v>
@@ -6606,7 +6610,7 @@
         <v>6</v>
       </c>
       <c r="F177" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G177">
         <v>1</v>
@@ -6620,13 +6624,13 @@
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A178" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B178">
         <v>4</v>
       </c>
       <c r="C178" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D178">
         <v>6</v>
@@ -6635,7 +6639,7 @@
         <v>7</v>
       </c>
       <c r="F178" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G178">
         <v>2</v>
@@ -6649,13 +6653,13 @@
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A179" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B179">
         <v>3</v>
       </c>
       <c r="C179" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D179">
         <v>4</v>
@@ -6664,7 +6668,7 @@
         <v>2</v>
       </c>
       <c r="F179" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G179">
         <v>2</v>
@@ -6678,13 +6682,13 @@
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A180" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B180">
         <v>4</v>
       </c>
       <c r="C180" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D180">
         <v>7</v>
@@ -6693,7 +6697,7 @@
         <v>0</v>
       </c>
       <c r="F180" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G180">
         <v>1</v>
@@ -6707,13 +6711,13 @@
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A181" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B181">
         <v>4</v>
       </c>
       <c r="C181" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D181">
         <v>7</v>
@@ -6722,7 +6726,7 @@
         <v>2</v>
       </c>
       <c r="F181" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G181">
         <v>2</v>
@@ -6736,13 +6740,13 @@
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A182" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B182">
         <v>3</v>
       </c>
       <c r="C182" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D182">
         <v>1</v>
@@ -6751,7 +6755,7 @@
         <v>7</v>
       </c>
       <c r="F182" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G182">
         <v>2</v>
@@ -6765,13 +6769,13 @@
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A183" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B183">
         <v>4</v>
       </c>
       <c r="C183" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D183">
         <v>6</v>
@@ -6780,7 +6784,7 @@
         <v>7</v>
       </c>
       <c r="F183" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="G183">
         <v>1</v>
@@ -6794,13 +6798,13 @@
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A184" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B184">
         <v>4</v>
       </c>
       <c r="C184" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D184">
         <v>7</v>
@@ -6809,7 +6813,7 @@
         <v>5</v>
       </c>
       <c r="F184" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G184">
         <v>1</v>
@@ -6823,13 +6827,13 @@
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A185" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B185">
         <v>4</v>
       </c>
       <c r="C185" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D185">
         <v>10</v>
@@ -6838,7 +6842,7 @@
         <v>0</v>
       </c>
       <c r="F185" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G185">
         <v>1</v>
@@ -6852,13 +6856,13 @@
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A186" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B186">
         <v>1</v>
       </c>
       <c r="C186" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D186">
         <v>4</v>
@@ -6867,7 +6871,7 @@
         <v>0</v>
       </c>
       <c r="F186" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="G186">
         <v>3</v>
@@ -6881,13 +6885,13 @@
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A187" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B187">
         <v>4</v>
       </c>
       <c r="C187" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D187">
         <v>10</v>
@@ -6896,7 +6900,7 @@
         <v>2</v>
       </c>
       <c r="F187" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G187">
         <v>1</v>
@@ -6910,13 +6914,13 @@
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A188" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B188">
         <v>1</v>
       </c>
       <c r="C188" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D188">
         <v>1</v>
@@ -6925,7 +6929,7 @@
         <v>0</v>
       </c>
       <c r="F188" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G188">
         <v>2</v>
@@ -6939,13 +6943,13 @@
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A189" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B189">
         <v>2</v>
       </c>
       <c r="C189" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D189">
         <v>8</v>
@@ -6954,7 +6958,7 @@
         <v>5</v>
       </c>
       <c r="F189" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G189">
         <v>1</v>
@@ -6968,13 +6972,13 @@
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A190" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B190">
         <v>3</v>
       </c>
       <c r="C190" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D190">
         <v>4</v>
@@ -6983,7 +6987,7 @@
         <v>7</v>
       </c>
       <c r="F190" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G190">
         <v>2</v>
@@ -6997,13 +7001,13 @@
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A191" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B191">
         <v>3</v>
       </c>
       <c r="C191" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D191">
         <v>5</v>
@@ -7012,7 +7016,7 @@
         <v>7</v>
       </c>
       <c r="F191" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="G191">
         <v>2</v>
@@ -7026,13 +7030,13 @@
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A192" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B192">
         <v>3</v>
       </c>
       <c r="C192" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D192">
         <v>2</v>
@@ -7041,7 +7045,7 @@
         <v>5</v>
       </c>
       <c r="F192" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="G192">
         <v>1</v>
@@ -7055,13 +7059,13 @@
     </row>
     <row r="193" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A193" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B193">
         <v>4</v>
       </c>
       <c r="C193" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D193">
         <v>8</v>
@@ -7070,7 +7074,7 @@
         <v>7</v>
       </c>
       <c r="F193" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G193">
         <v>1</v>
@@ -7084,13 +7088,13 @@
     </row>
     <row r="194" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A194" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B194">
         <v>1</v>
       </c>
       <c r="C194" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D194">
         <v>3</v>
@@ -7099,7 +7103,7 @@
         <v>5</v>
       </c>
       <c r="F194" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G194">
         <v>1</v>
@@ -7113,13 +7117,13 @@
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A195" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B195">
         <v>4</v>
       </c>
       <c r="C195" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D195">
         <v>9</v>
@@ -7128,7 +7132,7 @@
         <v>2</v>
       </c>
       <c r="F195" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G195">
         <v>1</v>
@@ -7142,13 +7146,13 @@
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A196" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B196">
         <v>1</v>
       </c>
       <c r="C196" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D196">
         <v>3</v>
@@ -7157,7 +7161,7 @@
         <v>5</v>
       </c>
       <c r="F196" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="G196">
         <v>2</v>
@@ -7171,13 +7175,13 @@
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A197" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B197">
         <v>3</v>
       </c>
       <c r="C197" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D197">
         <v>5</v>
@@ -7186,7 +7190,7 @@
         <v>1</v>
       </c>
       <c r="F197" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G197">
         <v>2</v>
@@ -7200,13 +7204,13 @@
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A198" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B198">
         <v>3</v>
       </c>
       <c r="C198" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D198">
         <v>3</v>
@@ -7215,7 +7219,7 @@
         <v>2</v>
       </c>
       <c r="F198" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G198">
         <v>2</v>
@@ -7229,13 +7233,13 @@
     </row>
     <row r="199" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A199" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B199">
         <v>2</v>
       </c>
       <c r="C199" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D199">
         <v>7</v>
@@ -7244,7 +7248,7 @@
         <v>0</v>
       </c>
       <c r="F199" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G199">
         <v>1</v>
@@ -7258,13 +7262,13 @@
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A200" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B200">
         <v>2</v>
       </c>
       <c r="C200" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D200">
         <v>6</v>
@@ -7273,7 +7277,7 @@
         <v>5</v>
       </c>
       <c r="F200" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G200">
         <v>3</v>
@@ -7287,13 +7291,13 @@
     </row>
     <row r="201" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A201" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B201">
         <v>1</v>
       </c>
       <c r="C201" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D201">
         <v>2</v>
@@ -7302,7 +7306,7 @@
         <v>7</v>
       </c>
       <c r="F201" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G201">
         <v>4</v>
@@ -7316,13 +7320,13 @@
     </row>
     <row r="202" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A202" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B202">
         <v>2</v>
       </c>
       <c r="C202" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D202">
         <v>9</v>
@@ -7331,7 +7335,7 @@
         <v>2</v>
       </c>
       <c r="F202" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="G202">
         <v>3</v>
@@ -7345,13 +7349,13 @@
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A203" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B203">
         <v>4</v>
       </c>
       <c r="C203" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D203">
         <v>8</v>
@@ -7360,7 +7364,7 @@
         <v>2</v>
       </c>
       <c r="F203" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G203">
         <v>1</v>
@@ -7374,13 +7378,13 @@
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A204" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B204">
         <v>4</v>
       </c>
       <c r="C204" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D204">
         <v>7</v>
@@ -7389,7 +7393,7 @@
         <v>7</v>
       </c>
       <c r="F204" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G204">
         <v>1</v>
@@ -7403,13 +7407,13 @@
     </row>
     <row r="205" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A205" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B205">
         <v>2</v>
       </c>
       <c r="C205" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D205">
         <v>9</v>
@@ -7418,7 +7422,7 @@
         <v>0</v>
       </c>
       <c r="F205" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G205">
         <v>1</v>
@@ -7432,13 +7436,13 @@
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A206" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B206">
         <v>4</v>
       </c>
       <c r="C206" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D206">
         <v>8</v>
@@ -7447,7 +7451,7 @@
         <v>7</v>
       </c>
       <c r="F206" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="G206">
         <v>2</v>
@@ -7461,13 +7465,13 @@
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A207" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B207">
         <v>4</v>
       </c>
       <c r="C207" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D207">
         <v>10</v>
@@ -7476,7 +7480,7 @@
         <v>0</v>
       </c>
       <c r="F207" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G207">
         <v>1</v>
@@ -7490,13 +7494,13 @@
     </row>
     <row r="208" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A208" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B208">
         <v>3</v>
       </c>
       <c r="C208" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D208">
         <v>4</v>
@@ -7505,7 +7509,7 @@
         <v>0</v>
       </c>
       <c r="F208" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G208">
         <v>1</v>
@@ -7519,13 +7523,13 @@
     </row>
     <row r="209" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A209" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B209">
         <v>3</v>
       </c>
       <c r="C209" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D209">
         <v>4</v>
@@ -7534,7 +7538,7 @@
         <v>2</v>
       </c>
       <c r="F209" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G209">
         <v>1</v>
@@ -7548,13 +7552,13 @@
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A210" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B210">
         <v>4</v>
       </c>
       <c r="C210" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D210">
         <v>6</v>
@@ -7563,7 +7567,7 @@
         <v>5</v>
       </c>
       <c r="F210" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G210">
         <v>1</v>
@@ -7577,13 +7581,13 @@
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A211" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B211">
         <v>3</v>
       </c>
       <c r="C211" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D211">
         <v>4</v>
@@ -7592,7 +7596,7 @@
         <v>0</v>
       </c>
       <c r="F211" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G211">
         <v>1</v>
@@ -7606,13 +7610,13 @@
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A212" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B212">
         <v>2</v>
       </c>
       <c r="C212" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D212">
         <v>8</v>
@@ -7621,7 +7625,7 @@
         <v>7</v>
       </c>
       <c r="F212" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="G212">
         <v>4</v>
@@ -7635,13 +7639,13 @@
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A213" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B213">
         <v>2</v>
       </c>
       <c r="C213" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D213">
         <v>9</v>
@@ -7650,7 +7654,7 @@
         <v>0</v>
       </c>
       <c r="F213" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G213">
         <v>4</v>
@@ -7664,13 +7668,13 @@
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A214" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B214">
         <v>4</v>
       </c>
       <c r="C214" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D214">
         <v>9</v>
@@ -7679,7 +7683,7 @@
         <v>0</v>
       </c>
       <c r="F214" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G214">
         <v>1</v>
@@ -7693,13 +7697,13 @@
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A215" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B215">
         <v>4</v>
       </c>
       <c r="C215" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D215">
         <v>10</v>
@@ -7708,7 +7712,7 @@
         <v>7</v>
       </c>
       <c r="F215" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G215">
         <v>1</v>
@@ -7722,13 +7726,13 @@
     </row>
     <row r="216" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A216" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B216">
         <v>3</v>
       </c>
       <c r="C216" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D216">
         <v>3</v>
@@ -7737,7 +7741,7 @@
         <v>5</v>
       </c>
       <c r="F216" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G216">
         <v>1</v>
@@ -7751,13 +7755,13 @@
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A217" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B217">
         <v>3</v>
       </c>
       <c r="C217" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D217">
         <v>1</v>
@@ -7766,7 +7770,7 @@
         <v>2</v>
       </c>
       <c r="F217" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G217">
         <v>1</v>
